--- a/artfynd/A 61242-2023 artfynd.xlsx
+++ b/artfynd/A 61242-2023 artfynd.xlsx
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130187646</v>
+        <v>130187634</v>
       </c>
       <c r="B10" t="n">
-        <v>79119</v>
+        <v>80135</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6434</v>
+        <v>6457</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>765694</v>
+        <v>765743</v>
       </c>
       <c r="R10" t="n">
-        <v>7203888</v>
+        <v>7203842</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130187634</v>
+        <v>130187646</v>
       </c>
       <c r="B11" t="n">
-        <v>80135</v>
+        <v>79119</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6457</v>
+        <v>6434</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>765743</v>
+        <v>765694</v>
       </c>
       <c r="R11" t="n">
-        <v>7203842</v>
+        <v>7203888</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 61242-2023 artfynd.xlsx
+++ b/artfynd/A 61242-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187648</v>
       </c>
       <c r="B2" t="n">
-        <v>80104</v>
+        <v>80189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130187661</v>
       </c>
       <c r="B3" t="n">
-        <v>80135</v>
+        <v>80220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130187652</v>
       </c>
       <c r="B4" t="n">
-        <v>85291</v>
+        <v>85378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130187655</v>
       </c>
       <c r="B5" t="n">
-        <v>83073</v>
+        <v>83158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>130187647</v>
       </c>
       <c r="B6" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>130187653</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>130187656</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>130187629</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130187634</v>
+        <v>130187646</v>
       </c>
       <c r="B10" t="n">
-        <v>80135</v>
+        <v>79204</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6457</v>
+        <v>6434</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>765743</v>
+        <v>765694</v>
       </c>
       <c r="R10" t="n">
-        <v>7203842</v>
+        <v>7203888</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130187646</v>
+        <v>130187634</v>
       </c>
       <c r="B11" t="n">
-        <v>79119</v>
+        <v>80220</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6434</v>
+        <v>6457</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>765694</v>
+        <v>765743</v>
       </c>
       <c r="R11" t="n">
-        <v>7203888</v>
+        <v>7203842</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 61242-2023 artfynd.xlsx
+++ b/artfynd/A 61242-2023 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130187655</v>
+        <v>130187647</v>
       </c>
       <c r="B5" t="n">
-        <v>83158</v>
+        <v>57985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>765728</v>
+        <v>765699</v>
       </c>
       <c r="R5" t="n">
-        <v>7203906</v>
+        <v>7203908</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130187647</v>
+        <v>130187655</v>
       </c>
       <c r="B6" t="n">
-        <v>57985</v>
+        <v>83158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>765699</v>
+        <v>765728</v>
       </c>
       <c r="R6" t="n">
-        <v>7203908</v>
+        <v>7203906</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 61242-2023 artfynd.xlsx
+++ b/artfynd/A 61242-2023 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130187647</v>
+        <v>130187655</v>
       </c>
       <c r="B5" t="n">
-        <v>57985</v>
+        <v>83158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>765699</v>
+        <v>765728</v>
       </c>
       <c r="R5" t="n">
-        <v>7203908</v>
+        <v>7203906</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130187655</v>
+        <v>130187647</v>
       </c>
       <c r="B6" t="n">
-        <v>83158</v>
+        <v>57985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>765728</v>
+        <v>765699</v>
       </c>
       <c r="R6" t="n">
-        <v>7203906</v>
+        <v>7203908</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 61242-2023 artfynd.xlsx
+++ b/artfynd/A 61242-2023 artfynd.xlsx
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130187646</v>
+        <v>130187634</v>
       </c>
       <c r="B10" t="n">
-        <v>79204</v>
+        <v>80220</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6434</v>
+        <v>6457</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>765694</v>
+        <v>765743</v>
       </c>
       <c r="R10" t="n">
-        <v>7203888</v>
+        <v>7203842</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130187634</v>
+        <v>130187646</v>
       </c>
       <c r="B11" t="n">
-        <v>80220</v>
+        <v>79204</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6457</v>
+        <v>6434</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>765743</v>
+        <v>765694</v>
       </c>
       <c r="R11" t="n">
-        <v>7203842</v>
+        <v>7203888</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 61242-2023 artfynd.xlsx
+++ b/artfynd/A 61242-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187648</v>
       </c>
       <c r="B2" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130187661</v>
       </c>
       <c r="B3" t="n">
-        <v>80220</v>
+        <v>80223</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130187652</v>
       </c>
       <c r="B4" t="n">
-        <v>85378</v>
+        <v>85381</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>130187655</v>
       </c>
       <c r="B6" t="n">
-        <v>83158</v>
+        <v>83161</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>130187653</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>130187656</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>130187629</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>130187634</v>
       </c>
       <c r="B10" t="n">
-        <v>80220</v>
+        <v>80223</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>130187646</v>
       </c>
       <c r="B11" t="n">
-        <v>79204</v>
+        <v>79207</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 61242-2023 artfynd.xlsx
+++ b/artfynd/A 61242-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187648</v>
       </c>
       <c r="B2" t="n">
-        <v>80192</v>
+        <v>80218</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130187661</v>
       </c>
       <c r="B3" t="n">
-        <v>80223</v>
+        <v>80249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130187652</v>
       </c>
       <c r="B4" t="n">
-        <v>85381</v>
+        <v>85407</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130187647</v>
+        <v>130187655</v>
       </c>
       <c r="B5" t="n">
-        <v>57985</v>
+        <v>83187</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>765699</v>
+        <v>765728</v>
       </c>
       <c r="R5" t="n">
-        <v>7203908</v>
+        <v>7203906</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130187655</v>
+        <v>130187647</v>
       </c>
       <c r="B6" t="n">
-        <v>83161</v>
+        <v>58011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>765728</v>
+        <v>765699</v>
       </c>
       <c r="R6" t="n">
-        <v>7203906</v>
+        <v>7203908</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1238,7 +1238,7 @@
         <v>130187653</v>
       </c>
       <c r="B7" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>130187656</v>
       </c>
       <c r="B8" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>130187629</v>
       </c>
       <c r="B9" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130187634</v>
+        <v>130187646</v>
       </c>
       <c r="B10" t="n">
-        <v>80223</v>
+        <v>79233</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6457</v>
+        <v>6434</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>765743</v>
+        <v>765694</v>
       </c>
       <c r="R10" t="n">
-        <v>7203842</v>
+        <v>7203888</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130187646</v>
+        <v>130187634</v>
       </c>
       <c r="B11" t="n">
-        <v>79207</v>
+        <v>80249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6434</v>
+        <v>6457</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>765694</v>
+        <v>765743</v>
       </c>
       <c r="R11" t="n">
-        <v>7203888</v>
+        <v>7203842</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 61242-2023 artfynd.xlsx
+++ b/artfynd/A 61242-2023 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130187655</v>
+        <v>130187647</v>
       </c>
       <c r="B5" t="n">
-        <v>83187</v>
+        <v>58011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>765728</v>
+        <v>765699</v>
       </c>
       <c r="R5" t="n">
-        <v>7203906</v>
+        <v>7203908</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130187647</v>
+        <v>130187655</v>
       </c>
       <c r="B6" t="n">
-        <v>58011</v>
+        <v>83187</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>765699</v>
+        <v>765728</v>
       </c>
       <c r="R6" t="n">
-        <v>7203908</v>
+        <v>7203906</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 61242-2023 artfynd.xlsx
+++ b/artfynd/A 61242-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>130187652</v>
       </c>
       <c r="B4" t="n">
-        <v>85407</v>
+        <v>85408</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130187647</v>
+        <v>130187655</v>
       </c>
       <c r="B5" t="n">
-        <v>58011</v>
+        <v>83188</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>765699</v>
+        <v>765728</v>
       </c>
       <c r="R5" t="n">
-        <v>7203908</v>
+        <v>7203906</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130187655</v>
+        <v>130187647</v>
       </c>
       <c r="B6" t="n">
-        <v>83187</v>
+        <v>58011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>765728</v>
+        <v>765699</v>
       </c>
       <c r="R6" t="n">
-        <v>7203906</v>
+        <v>7203908</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 61242-2023 artfynd.xlsx
+++ b/artfynd/A 61242-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>130187652</v>
       </c>
       <c r="B4" t="n">
-        <v>85408</v>
+        <v>85409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130187655</v>
+        <v>130187647</v>
       </c>
       <c r="B5" t="n">
-        <v>83188</v>
+        <v>58011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>765728</v>
+        <v>765699</v>
       </c>
       <c r="R5" t="n">
-        <v>7203906</v>
+        <v>7203908</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130187647</v>
+        <v>130187655</v>
       </c>
       <c r="B6" t="n">
-        <v>58011</v>
+        <v>83189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>765699</v>
+        <v>765728</v>
       </c>
       <c r="R6" t="n">
-        <v>7203908</v>
+        <v>7203906</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 61242-2023 artfynd.xlsx
+++ b/artfynd/A 61242-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187648</v>
       </c>
       <c r="B2" t="n">
-        <v>80218</v>
+        <v>80220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130187661</v>
       </c>
       <c r="B3" t="n">
-        <v>80249</v>
+        <v>80251</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130187652</v>
       </c>
       <c r="B4" t="n">
-        <v>85409</v>
+        <v>85411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130187647</v>
       </c>
       <c r="B5" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>130187655</v>
       </c>
       <c r="B6" t="n">
-        <v>83189</v>
+        <v>83191</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>130187653</v>
       </c>
       <c r="B7" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>130187656</v>
       </c>
       <c r="B8" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>130187629</v>
       </c>
       <c r="B9" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>130187646</v>
       </c>
       <c r="B10" t="n">
-        <v>79233</v>
+        <v>79235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>130187634</v>
       </c>
       <c r="B11" t="n">
-        <v>80249</v>
+        <v>80251</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 61242-2023 artfynd.xlsx
+++ b/artfynd/A 61242-2023 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130187647</v>
+        <v>130187655</v>
       </c>
       <c r="B5" t="n">
-        <v>58013</v>
+        <v>83191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>765699</v>
+        <v>765728</v>
       </c>
       <c r="R5" t="n">
-        <v>7203908</v>
+        <v>7203906</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130187655</v>
+        <v>130187647</v>
       </c>
       <c r="B6" t="n">
-        <v>83191</v>
+        <v>58013</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>765728</v>
+        <v>765699</v>
       </c>
       <c r="R6" t="n">
-        <v>7203906</v>
+        <v>7203908</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 61242-2023 artfynd.xlsx
+++ b/artfynd/A 61242-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130187648</v>
+        <v>130187652</v>
       </c>
       <c r="B2" t="n">
-        <v>80220</v>
+        <v>85534</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>241</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>765726</v>
+        <v>765734</v>
       </c>
       <c r="R2" t="n">
-        <v>7203954</v>
+        <v>7203925</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130187661</v>
+        <v>130187629</v>
       </c>
       <c r="B3" t="n">
-        <v>80251</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>765752</v>
+        <v>765724</v>
       </c>
       <c r="R3" t="n">
-        <v>7203847</v>
+        <v>7203886</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130187652</v>
+        <v>130187653</v>
       </c>
       <c r="B4" t="n">
-        <v>85411</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>241</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Shear</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>765734</v>
+        <v>765730</v>
       </c>
       <c r="R4" t="n">
-        <v>7203925</v>
+        <v>7203914</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,32 +1011,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130187655</v>
+        <v>130187656</v>
       </c>
       <c r="B5" t="n">
-        <v>83191</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>765728</v>
+        <v>765734</v>
       </c>
       <c r="R5" t="n">
-        <v>7203906</v>
+        <v>7203874</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,32 +1123,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130187647</v>
+        <v>130187646</v>
       </c>
       <c r="B6" t="n">
-        <v>58013</v>
+        <v>79351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6434</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>765699</v>
+        <v>765694</v>
       </c>
       <c r="R6" t="n">
-        <v>7203908</v>
+        <v>7203888</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130187653</v>
+        <v>130187655</v>
       </c>
       <c r="B7" t="n">
-        <v>79211</v>
+        <v>83307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>765730</v>
+        <v>765728</v>
       </c>
       <c r="R7" t="n">
-        <v>7203914</v>
+        <v>7203906</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,32 +1347,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130187656</v>
+        <v>130187648</v>
       </c>
       <c r="B8" t="n">
-        <v>79211</v>
+        <v>80336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>765734</v>
+        <v>765726</v>
       </c>
       <c r="R8" t="n">
-        <v>7203874</v>
+        <v>7203954</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130187629</v>
+        <v>130187634</v>
       </c>
       <c r="B9" t="n">
-        <v>79211</v>
+        <v>80367</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>765724</v>
+        <v>765743</v>
       </c>
       <c r="R9" t="n">
-        <v>7203886</v>
+        <v>7203842</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130187646</v>
+        <v>130187661</v>
       </c>
       <c r="B10" t="n">
-        <v>79235</v>
+        <v>80367</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6434</v>
+        <v>6457</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>765694</v>
+        <v>765752</v>
       </c>
       <c r="R10" t="n">
-        <v>7203888</v>
+        <v>7203847</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130187634</v>
+        <v>130187636</v>
       </c>
       <c r="B11" t="n">
-        <v>80251</v>
+        <v>80468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6457</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>765743</v>
+        <v>765680</v>
       </c>
       <c r="R11" t="n">
-        <v>7203842</v>
+        <v>7203916</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,6 +1792,444 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>110644199</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>skellefteå, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>765728</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7203895</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2 sovgropar</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>110644200</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>skellefteå, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>765805</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7203742</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>10 sovgropar</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130187647</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Boden-Skellefteå, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>765699</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7203908</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>NVI (C250260) Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130187631</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Boden-Skellefteå, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>765687</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7203841</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>NVI (C250260) Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61242-2023 artfynd.xlsx
+++ b/artfynd/A 61242-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187652</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187629</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187653</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187656</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187646</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187655</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,6 +1491,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187648</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1568,6 +1608,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187634</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1680,6 +1725,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187661</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1792,6 +1842,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187636</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1899,6 +1954,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110644199</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2006,6 +2066,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110644200</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2118,6 +2183,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187647</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2230,8 +2300,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187631</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>